--- a/assets/constructions/examples/ctd_arbm_pullstud.xlsx
+++ b/assets/constructions/examples/ctd_arbm_pullstud.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,37 +554,57 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PS-B50C-45-001</t>
+          <t>PS-P</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pull stud</t>
+          <t>for BT50 MITISUI SEIKI</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
@@ -596,104 +616,92 @@
       <c r="L2" t="n">
         <v>25</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>SAND_PS-B50C</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>SANDVIK</t>
-        </is>
-      </c>
+          <t>JIS_B_6339_MAS_403:BT50</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>MACHINE</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2021/YG1-TOOLING</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>7</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>MACHINE</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>30</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>каталог Sandvik/Вращающиеся инструменты 2020</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PS-5</t>
+          <t>BT40C-60</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>YG1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>BT50-Ⅰ STANDARD TYPE</t>
-        </is>
-      </c>
+          <t>AMATI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
-      </c>
-      <c r="G3" t="n">
-        <v>38</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>17</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>28</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>M16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>JIS_B_6339_MAS_403:BT50</t>
+          <t>JIS_B_6339_MAS_403:BT40</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
@@ -715,42 +723,44 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021/YG1-TOOLING</t>
-        </is>
-      </c>
+          <t>2025 / AMATI Инструментальная и технологическая оснастка</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PS-I50C-45-001</t>
+          <t>BT50C-60</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Pull stud</t>
-        </is>
-      </c>
+          <t>AMATI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" t="n">
         <v>45</v>
       </c>
-      <c r="F4" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="G4" t="n">
-        <v>37</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="I4" t="n">
+        <v>35</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>M24</t>
@@ -760,58 +770,50 @@
       <c r="L4" t="n">
         <v>25</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>SAND_PS-I50C</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>SANDVIK</t>
-        </is>
-      </c>
+          <t>JIS_B_6339_MAS_403:BT50</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>29.1</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>MACHINE</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025 / AMATI Инструментальная и технологическая оснастка</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
-        <v>11</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>MACHINE</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="W4" t="n">
-        <v>30</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>каталог Sandvik/Вращающиеся инструменты 2020</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PS-B40-45-001</t>
+          <t>PS-I50C-45-001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -825,38 +827,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
         <v>45</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>25.5</v>
       </c>
       <c r="G5" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>19.6</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>M16</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>SAND_PS-B40</t>
+          <t>SAND_PS-I50C</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>JIS_B_6339_MAS_403:BT40</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -865,15 +867,17 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>29.1</v>
       </c>
       <c r="Q5" t="b">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>11</v>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>MACHINE</t>
@@ -881,10 +885,10 @@
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="W5" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -894,11 +898,17 @@
           <t>каталог Sandvik/Вращающиеся инструменты 2020</t>
         </is>
       </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAT50-45UC</t>
+          <t>BT40-90C</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -906,62 +916,56 @@
           <t>DEREK</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Штревели CAT</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E6" t="n">
+        <v>90</v>
+      </c>
       <c r="F6" t="n">
-        <v>25.4</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>36.5</v>
+        <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>20.8</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>17.7</v>
+        <v>28</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1" - 8 UNC</t>
+          <t>M16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
+        <v>17</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>JIS_B_6339_MAS_403:BT40</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>DEREK</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>DER_PULL-45</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>CAT_50</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="n">
-        <v>11.9</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -970,9 +974,11 @@
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="W6" t="n">
+        <v>19</v>
+      </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
@@ -981,6 +987,12 @@
           <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
         </is>
       </c>
+      <c r="Z6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
